--- a/practice_difficulty.xlsx
+++ b/practice_difficulty.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hackerman/misty_py/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LabUser\Documents\misty_py-studyBranch\misty_py-studyBranch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D521F46-C37B-3044-856A-07A767F8E25A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ED703BD-60E8-4A5A-9140-695BFA3A3450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5180" yWindow="1800" windowWidth="28040" windowHeight="17440" xr2:uid="{3837BCBD-2ED0-4640-AE45-77FF68A549D1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3837BCBD-2ED0-4640-AE45-77FF68A549D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,12 +36,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="3">
   <si>
     <t>prac_diff</t>
   </si>
   <si>
     <t>easy1</t>
+  </si>
+  <si>
+    <t>prac_time</t>
   </si>
 </sst>
 </file>
@@ -413,27 +416,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64E86046-B6D7-4E43-BEFF-471E6D8160A2}">
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>30</v>
+      </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
+      <c r="B3">
+        <v>15</v>
+      </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
